--- a/Módulos & Componentes.xlsx
+++ b/Módulos & Componentes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
   <si>
     <t>Desarrollador</t>
   </si>
@@ -38,6 +38,15 @@
   </si>
   <si>
     <t>Módulos</t>
+  </si>
+  <si>
+    <t>Filtrar por roles - biblioteca</t>
+  </si>
+  <si>
+    <t>listo</t>
+  </si>
+  <si>
+    <t>Filtrar por UserId - pages-02</t>
   </si>
 </sst>
 </file>
@@ -81,9 +90,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -396,11 +408,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="6" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" style="2" customWidth="1"/>
+    <col min="2" max="6" width="14.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -421,6 +433,37 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Módulos & Componentes.xlsx
+++ b/Módulos & Componentes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Componentes" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
   <si>
     <t>Desarrollador</t>
   </si>
@@ -40,20 +40,59 @@
     <t>Módulos</t>
   </si>
   <si>
-    <t>Filtrar por roles - biblioteca</t>
-  </si>
-  <si>
     <t>listo</t>
   </si>
   <si>
-    <t>Filtrar por UserId - pages-02</t>
+    <t>/components/nav-header</t>
+  </si>
+  <si>
+    <t>/users/role/pages-02/components</t>
+  </si>
+  <si>
+    <t>filterByAuthUser - pages-02</t>
+  </si>
+  <si>
+    <t>nav-header (modular - role dinamico)</t>
+  </si>
+  <si>
+    <t>middle-section /pages-02 (modular)</t>
+  </si>
+  <si>
+    <t>middle-section Modular (Titulo Dinamico)</t>
+  </si>
+  <si>
+    <t>console log (getUserRole)</t>
+  </si>
+  <si>
+    <t>en los script principales</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>filterDataByRole - biblioteca</t>
+  </si>
+  <si>
+    <t>/modules/tabla/filterData/filterByAuthUser.js</t>
+  </si>
+  <si>
+    <t>/modules/tabla/filterData/filterDataByRole.js</t>
+  </si>
+  <si>
+    <t>/components/month-buttons/month-buttons.js</t>
+  </si>
+  <si>
+    <t>month-buttons modular (botton-según rol)</t>
+  </si>
+  <si>
+    <t>/components/middle-section/middle-section.js</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,6 +107,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -90,13 +143,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -378,13 +440,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:F1"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="6" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="6" width="17.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="50.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -394,28 +459,98 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
     <col min="2" max="6" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -435,35 +570,73 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
